--- a/artfynd/S 1063-2025 artfynd.xlsx
+++ b/artfynd/S 1063-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80787856</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102530836</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532838</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103288993</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103288994</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503680</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102533403</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102530834</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80787853</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1705,6 +1755,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80787854</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1815,6 +1870,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80787855</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102530842</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2017,6 +2082,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102533373</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,6 +2189,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102523919</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2220,6 +2295,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102530884</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2321,6 +2401,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532287</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2431,6 +2516,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80787852</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2532,6 +2622,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102533007</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2633,6 +2728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102533407</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2734,6 +2834,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102530858</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2835,6 +2940,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532272</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2936,6 +3046,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532273</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3037,6 +3152,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102533380</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3138,6 +3258,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532271</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3239,6 +3364,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532844</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3349,6 +3479,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80787851</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3465,6 +3600,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126679261</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3566,6 +3706,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103288971</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3667,6 +3812,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102530871</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3768,6 +3918,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102530872</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3869,6 +4024,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532848</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3970,6 +4130,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532850</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4071,6 +4236,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102533029</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4172,6 +4342,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102533924</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4273,6 +4448,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102533931</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4374,6 +4554,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103288992</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4475,6 +4660,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103288995</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4576,6 +4766,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103288996</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4677,6 +4872,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102532852</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4774,6 +4974,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503667</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4876,6 +5081,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102523807</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4977,8 +5187,57 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2022 Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102530844</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>